--- a/source/spreadsheets/Neoverse_for_Claude.xlsx
+++ b/source/spreadsheets/Neoverse_for_Claude.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cmestes87/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5EF43C-9524-E04E-A49E-5372E82AC6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D8630A-A4AD-834C-8603-321D4472ABFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40500" yWindow="2020" windowWidth="26840" windowHeight="15680" xr2:uid="{BF29D5B1-F294-134E-8F7B-70D5B4D848F8}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17960" xr2:uid="{BF29D5B1-F294-134E-8F7B-70D5B4D848F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 (2)" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="148">
   <si>
     <t>Neoverse Interactive Edition</t>
   </si>
@@ -474,6 +474,15 @@
   </si>
   <si>
     <t>Playlists</t>
+  </si>
+  <si>
+    <t>Tribal Lines</t>
+  </si>
+  <si>
+    <t>Tribal Motif</t>
+  </si>
+  <si>
+    <t>Tribal Shapes</t>
   </si>
 </sst>
 </file>
@@ -860,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7152A363-982E-1044-8657-DA2C0F17B383}">
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
@@ -2184,7 +2193,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="B100" t="s">
         <v>6</v>
@@ -2198,7 +2207,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="B101" t="s">
         <v>6</v>
@@ -2212,7 +2221,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="B102" t="s">
         <v>6</v>
@@ -2224,14 +2233,37 @@
         <v>7</v>
       </c>
     </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="1" t="s">
-        <v>105</v>
+      <c r="A104" t="s">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B105" t="s">
         <v>6</v>
@@ -2243,37 +2275,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
-        <v>107</v>
-      </c>
-      <c r="B106" t="s">
-        <v>6</v>
-      </c>
-      <c r="C106" t="s">
-        <v>6</v>
-      </c>
-      <c r="D106" t="s">
-        <v>7</v>
-      </c>
-    </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
-        <v>108</v>
-      </c>
-      <c r="B107" t="s">
-        <v>6</v>
-      </c>
-      <c r="C107" t="s">
-        <v>6</v>
-      </c>
-      <c r="D107" t="s">
-        <v>7</v>
+      <c r="A107" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B108" t="s">
         <v>6</v>
@@ -2287,13 +2296,13 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B109" t="s">
         <v>6</v>
       </c>
       <c r="C109" t="s">
-        <v>142</v>
+        <v>6</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -2301,7 +2310,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B110" t="s">
         <v>6</v>
@@ -2315,13 +2324,13 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B111" t="s">
         <v>6</v>
       </c>
       <c r="C111" t="s">
-        <v>142</v>
+        <v>6</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -2329,13 +2338,13 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B112" t="s">
         <v>6</v>
       </c>
       <c r="C112" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -2343,7 +2352,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B113" t="s">
         <v>6</v>
@@ -2357,13 +2366,13 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B114" t="s">
         <v>6</v>
       </c>
       <c r="C114" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -2371,7 +2380,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B115" t="s">
         <v>6</v>
@@ -2383,68 +2392,70 @@
         <v>7</v>
       </c>
     </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>114</v>
+      </c>
+      <c r="B116" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" t="s">
+        <v>6</v>
+      </c>
+      <c r="D116" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A117" s="1" t="s">
-        <v>117</v>
+      <c r="A117" t="s">
+        <v>115</v>
+      </c>
+      <c r="B117" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" t="s">
+        <v>6</v>
+      </c>
+      <c r="D117" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
+        <v>116</v>
+      </c>
+      <c r="B118" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" t="s">
+        <v>6</v>
+      </c>
+      <c r="D118" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
         <v>118</v>
       </c>
-      <c r="B118" t="s">
-        <v>6</v>
-      </c>
-      <c r="C118" t="s">
-        <v>6</v>
-      </c>
-      <c r="D118" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
-        <v>119</v>
-      </c>
-      <c r="B119" t="s">
-        <v>6</v>
-      </c>
-      <c r="C119" t="s">
-        <v>6</v>
-      </c>
-      <c r="D119" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
-        <v>120</v>
-      </c>
-      <c r="B120" t="s">
-        <v>6</v>
-      </c>
-      <c r="C120" t="s">
-        <v>6</v>
-      </c>
-      <c r="D120" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D121" s="2"/>
+      <c r="B121" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" t="s">
+        <v>6</v>
+      </c>
+      <c r="D121" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B122" t="s">
         <v>6</v>
@@ -2457,34 +2468,34 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D123" s="2"/>
+      <c r="A123" t="s">
+        <v>120</v>
+      </c>
+      <c r="B123" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" t="s">
+        <v>6</v>
+      </c>
+      <c r="D123" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
-        <v>124</v>
-      </c>
-      <c r="B124" t="s">
-        <v>6</v>
-      </c>
-      <c r="C124" t="s">
-        <v>6</v>
-      </c>
-      <c r="D124" t="s">
-        <v>7</v>
-      </c>
+      <c r="A124" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D124" s="2"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B125" t="s">
         <v>6</v>
@@ -2497,22 +2508,20 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
-        <v>126</v>
-      </c>
-      <c r="B126" t="s">
-        <v>6</v>
-      </c>
-      <c r="C126" t="s">
-        <v>6</v>
-      </c>
-      <c r="D126" t="s">
-        <v>7</v>
-      </c>
+      <c r="A126" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D126" s="2"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B127" t="s">
         <v>6</v>
@@ -2526,7 +2535,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B128" t="s">
         <v>6</v>
@@ -2540,7 +2549,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B129" t="s">
         <v>6</v>
@@ -2554,7 +2563,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B130" t="s">
         <v>6</v>
@@ -2568,7 +2577,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B131" t="s">
         <v>6</v>
@@ -2582,7 +2591,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B132" t="s">
         <v>6</v>
@@ -2594,72 +2603,76 @@
         <v>7</v>
       </c>
     </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>130</v>
+      </c>
+      <c r="B133" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" t="s">
+        <v>6</v>
+      </c>
+      <c r="D133" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A134" s="1" t="s">
-        <v>133</v>
+      <c r="A134" t="s">
+        <v>131</v>
+      </c>
+      <c r="B134" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" t="s">
+        <v>6</v>
+      </c>
+      <c r="D134" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
+        <v>132</v>
+      </c>
+      <c r="B135" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
         <v>134</v>
       </c>
-      <c r="B135" t="s">
-        <v>6</v>
-      </c>
-      <c r="C135" t="s">
+      <c r="B138" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" t="s">
         <v>142</v>
       </c>
-      <c r="D135" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
-        <v>135</v>
-      </c>
-      <c r="B136" t="s">
-        <v>6</v>
-      </c>
-      <c r="C136" t="s">
-        <v>142</v>
-      </c>
-      <c r="D136" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A137" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D137" s="2"/>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A138" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D138" s="2"/>
+      <c r="D138" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B139" t="s">
         <v>6</v>
       </c>
       <c r="C139" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -2667,64 +2680,102 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D140" s="2"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D141" s="2"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>138</v>
+      </c>
+      <c r="B142" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" t="s">
+        <v>6</v>
+      </c>
+      <c r="D142" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D140" s="2"/>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
+      <c r="B143" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D143" s="2"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
         <v>140</v>
       </c>
-      <c r="B141" t="s">
-        <v>6</v>
-      </c>
-      <c r="C141" t="s">
-        <v>6</v>
-      </c>
-      <c r="D141" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A142" s="2" t="s">
+      <c r="B144" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" t="s">
+        <v>6</v>
+      </c>
+      <c r="D144" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D142" s="2"/>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
+      <c r="B145" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D145" s="2"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
         <v>143</v>
       </c>
-      <c r="B143" t="s">
-        <v>6</v>
-      </c>
-      <c r="C143" t="s">
-        <v>6</v>
-      </c>
-      <c r="D143" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A144" s="2" t="s">
+      <c r="B146" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" t="s">
+        <v>6</v>
+      </c>
+      <c r="D146" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C144" s="2" t="s">
+      <c r="B147" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/source/spreadsheets/Neoverse_for_Claude.xlsx
+++ b/source/spreadsheets/Neoverse_for_Claude.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cmestes87/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D8630A-A4AD-834C-8603-321D4472ABFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F05B0A-3873-CA4B-8E68-CA8532B5C801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17960" xr2:uid="{BF29D5B1-F294-134E-8F7B-70D5B4D848F8}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{BF29D5B1-F294-134E-8F7B-70D5B4D848F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 (2)" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="151">
   <si>
     <t>Neoverse Interactive Edition</t>
   </si>
@@ -483,6 +483,15 @@
   </si>
   <si>
     <t>Tribal Shapes</t>
+  </si>
+  <si>
+    <t>Requires SuperTouch</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>Feature</t>
   </si>
 </sst>
 </file>
@@ -869,16 +878,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7152A363-982E-1044-8657-DA2C0F17B383}">
-  <dimension ref="A1:E147"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="18.6640625" customWidth="1"/>
+    <col min="4" max="6" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -891,13 +900,22 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -913,8 +931,14 @@
       <c r="E3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -927,8 +951,14 @@
       <c r="D4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -944,8 +974,17 @@
       <c r="E5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>54</v>
       </c>
@@ -961,8 +1000,14 @@
       <c r="E6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -975,8 +1020,14 @@
       <c r="D7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>56</v>
       </c>
@@ -989,8 +1040,14 @@
       <c r="D8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -1003,8 +1060,14 @@
       <c r="D9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -1017,8 +1080,14 @@
       <c r="D10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -1031,8 +1100,14 @@
       <c r="D11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1045,8 +1120,14 @@
       <c r="D12" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -1059,8 +1140,14 @@
       <c r="D13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -1073,8 +1160,14 @@
       <c r="D14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -1087,8 +1180,14 @@
       <c r="D15" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>64</v>
       </c>
@@ -1101,8 +1200,14 @@
       <c r="D16" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>65</v>
       </c>
@@ -1118,8 +1223,14 @@
       <c r="E17" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -1135,8 +1246,14 @@
       <c r="E18" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -1149,8 +1266,14 @@
       <c r="D19" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -1163,8 +1286,14 @@
       <c r="D20" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>69</v>
       </c>
@@ -1177,8 +1306,14 @@
       <c r="D21" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -1191,8 +1326,14 @@
       <c r="D22" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>71</v>
       </c>
@@ -1208,13 +1349,22 @@
       <c r="E23" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -1227,8 +1377,14 @@
       <c r="D26" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -1241,8 +1397,14 @@
       <c r="D27" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
@@ -1253,8 +1415,14 @@
         <v>6</v>
       </c>
       <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>10</v>
       </c>
@@ -1265,8 +1433,14 @@
         <v>6</v>
       </c>
       <c r="D29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -1279,8 +1453,14 @@
       <c r="D30" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1293,8 +1473,14 @@
       <c r="D31" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -1307,8 +1493,14 @@
       <c r="D32" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -1321,8 +1513,14 @@
       <c r="D33" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -1335,8 +1533,14 @@
       <c r="D34" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>16</v>
       </c>
@@ -1347,8 +1551,14 @@
         <v>6</v>
       </c>
       <c r="D35" s="2"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -1361,8 +1571,14 @@
       <c r="D36" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -1375,8 +1591,14 @@
       <c r="D37" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -1389,8 +1611,14 @@
       <c r="D38" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>20</v>
       </c>
@@ -1403,8 +1631,14 @@
       <c r="D39" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -1417,8 +1651,14 @@
       <c r="D40" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>22</v>
       </c>
@@ -1431,8 +1671,14 @@
       <c r="D41" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -1445,8 +1691,14 @@
       <c r="D42" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>24</v>
       </c>
@@ -1457,8 +1709,14 @@
         <v>6</v>
       </c>
       <c r="D43" s="2"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>25</v>
       </c>
@@ -1469,8 +1727,14 @@
         <v>6</v>
       </c>
       <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>26</v>
       </c>
@@ -1483,8 +1747,14 @@
       <c r="D45" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>27</v>
       </c>
@@ -1497,8 +1767,14 @@
       <c r="D46" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>28</v>
       </c>
@@ -1509,8 +1785,14 @@
         <v>6</v>
       </c>
       <c r="D47" s="2"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>29</v>
       </c>
@@ -1523,8 +1805,14 @@
       <c r="D48" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>30</v>
       </c>
@@ -1537,8 +1825,14 @@
       <c r="D49" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>31</v>
       </c>
@@ -1549,8 +1843,14 @@
         <v>6</v>
       </c>
       <c r="D50" s="2"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1563,8 +1863,14 @@
       <c r="D51" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>33</v>
       </c>
@@ -1577,8 +1883,14 @@
       <c r="D52" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>34</v>
       </c>
@@ -1591,8 +1903,14 @@
       <c r="D53" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>35</v>
       </c>
@@ -1605,8 +1923,14 @@
       <c r="D54" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>36</v>
       </c>
@@ -1619,8 +1943,14 @@
       <c r="D55" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>37</v>
       </c>
@@ -1631,8 +1961,14 @@
         <v>6</v>
       </c>
       <c r="D56" s="2"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>38</v>
       </c>
@@ -1645,8 +1981,14 @@
       <c r="D57" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>39</v>
       </c>
@@ -1659,8 +2001,14 @@
       <c r="D58" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -1673,8 +2021,14 @@
       <c r="D59" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>41</v>
       </c>
@@ -1687,8 +2041,14 @@
       <c r="D60" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>42</v>
       </c>
@@ -1701,8 +2061,14 @@
       <c r="D61" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>43</v>
       </c>
@@ -1715,8 +2081,14 @@
       <c r="D62" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>44</v>
       </c>
@@ -1729,8 +2101,14 @@
       <c r="D63" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>45</v>
       </c>
@@ -1743,8 +2121,14 @@
       <c r="D64" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>46</v>
       </c>
@@ -1757,8 +2141,14 @@
       <c r="D65" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>47</v>
       </c>
@@ -1771,8 +2161,14 @@
       <c r="D66" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>48</v>
       </c>
@@ -1785,8 +2181,14 @@
       <c r="D67" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>49</v>
       </c>
@@ -1799,13 +2201,19 @@
       <c r="D68" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -1818,8 +2226,14 @@
       <c r="D71" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -1832,8 +2246,14 @@
       <c r="D72" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>75</v>
       </c>
@@ -1844,8 +2264,14 @@
         <v>6</v>
       </c>
       <c r="D73" s="2"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -1858,8 +2284,14 @@
       <c r="D74" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -1872,8 +2304,14 @@
       <c r="D75" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -1886,8 +2324,14 @@
       <c r="D76" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -1900,8 +2344,14 @@
       <c r="D77" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -1914,8 +2364,14 @@
       <c r="D78" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>81</v>
       </c>
@@ -1926,8 +2382,14 @@
         <v>6</v>
       </c>
       <c r="D79" s="2"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -1940,8 +2402,14 @@
       <c r="D80" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>83</v>
       </c>
@@ -1952,8 +2420,14 @@
         <v>6</v>
       </c>
       <c r="D81" s="2"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>84</v>
       </c>
@@ -1964,8 +2438,14 @@
         <v>6</v>
       </c>
       <c r="D82" s="2"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -1978,8 +2458,14 @@
       <c r="D83" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -1992,8 +2478,14 @@
       <c r="D84" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -2006,8 +2498,14 @@
       <c r="D85" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -2020,8 +2518,14 @@
       <c r="D86" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>89</v>
       </c>
@@ -2034,8 +2538,14 @@
       <c r="D87" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>90</v>
       </c>
@@ -2048,8 +2558,14 @@
       <c r="D88" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -2062,8 +2578,14 @@
       <c r="D89" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>92</v>
       </c>
@@ -2074,8 +2596,14 @@
         <v>6</v>
       </c>
       <c r="D90" s="2"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>93</v>
       </c>
@@ -2086,8 +2614,14 @@
         <v>6</v>
       </c>
       <c r="D91" s="2"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -2100,8 +2634,14 @@
       <c r="D92" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -2114,8 +2654,14 @@
       <c r="D93" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>96</v>
       </c>
@@ -2126,8 +2672,14 @@
         <v>6</v>
       </c>
       <c r="D94" s="2"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -2140,8 +2692,14 @@
       <c r="D95" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>98</v>
       </c>
@@ -2152,8 +2710,14 @@
         <v>6</v>
       </c>
       <c r="D96" s="2"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>99</v>
       </c>
@@ -2164,8 +2728,14 @@
         <v>6</v>
       </c>
       <c r="D97" s="2"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>100</v>
       </c>
@@ -2178,8 +2748,14 @@
       <c r="D98" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>101</v>
       </c>
@@ -2190,8 +2766,14 @@
         <v>6</v>
       </c>
       <c r="D99" s="2"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>145</v>
       </c>
@@ -2204,8 +2786,14 @@
       <c r="D100" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>146</v>
       </c>
@@ -2218,8 +2806,14 @@
       <c r="D101" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>147</v>
       </c>
@@ -2232,8 +2826,14 @@
       <c r="D102" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -2246,8 +2846,14 @@
       <c r="D103" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -2260,8 +2866,14 @@
       <c r="D104" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -2274,13 +2886,19 @@
       <c r="D105" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>106</v>
       </c>
@@ -2293,8 +2911,14 @@
       <c r="D108" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G108">
+        <v>1</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -2307,8 +2931,14 @@
       <c r="D109" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G109">
+        <v>1</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -2321,8 +2951,14 @@
       <c r="D110" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -2335,8 +2971,14 @@
       <c r="D111" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>110</v>
       </c>
@@ -2349,8 +2991,14 @@
       <c r="D112" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G112">
+        <v>1</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>111</v>
       </c>
@@ -2363,8 +3011,14 @@
       <c r="D113" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G113">
+        <v>1</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>112</v>
       </c>
@@ -2377,8 +3031,14 @@
       <c r="D114" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G114">
+        <v>1</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>113</v>
       </c>
@@ -2391,8 +3051,14 @@
       <c r="D115" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G115">
+        <v>1</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>114</v>
       </c>
@@ -2405,8 +3071,14 @@
       <c r="D116" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G116">
+        <v>1</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>115</v>
       </c>
@@ -2419,8 +3091,14 @@
       <c r="D117" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G117">
+        <v>1</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>116</v>
       </c>
@@ -2433,13 +3111,19 @@
       <c r="D118" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G118">
+        <v>1</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>118</v>
       </c>
@@ -2452,8 +3136,14 @@
       <c r="D121" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G121">
+        <v>1</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>119</v>
       </c>
@@ -2466,8 +3156,14 @@
       <c r="D122" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G122">
+        <v>1</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>120</v>
       </c>
@@ -2480,8 +3176,14 @@
       <c r="D123" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G123">
+        <v>1</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>121</v>
       </c>
@@ -2492,8 +3194,14 @@
         <v>6</v>
       </c>
       <c r="D124" s="2"/>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>122</v>
       </c>
@@ -2506,8 +3214,14 @@
       <c r="D125" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G125">
+        <v>1</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>123</v>
       </c>
@@ -2518,8 +3232,14 @@
         <v>6</v>
       </c>
       <c r="D126" s="2"/>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G126">
+        <v>1</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>124</v>
       </c>
@@ -2532,8 +3252,14 @@
       <c r="D127" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G127">
+        <v>1</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>125</v>
       </c>
@@ -2546,8 +3272,14 @@
       <c r="D128" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G128">
+        <v>1</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>126</v>
       </c>
@@ -2560,8 +3292,14 @@
       <c r="D129" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G129">
+        <v>1</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>127</v>
       </c>
@@ -2574,8 +3312,14 @@
       <c r="D130" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G130">
+        <v>1</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>128</v>
       </c>
@@ -2588,8 +3332,14 @@
       <c r="D131" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>129</v>
       </c>
@@ -2602,8 +3352,14 @@
       <c r="D132" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G132">
+        <v>1</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>130</v>
       </c>
@@ -2616,8 +3372,14 @@
       <c r="D133" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>131</v>
       </c>
@@ -2630,8 +3392,14 @@
       <c r="D134" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>132</v>
       </c>
@@ -2644,13 +3412,19 @@
       <c r="D135" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G135">
+        <v>1</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>134</v>
       </c>
@@ -2663,8 +3437,14 @@
       <c r="D138" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>135</v>
       </c>
@@ -2677,8 +3457,14 @@
       <c r="D139" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>136</v>
       </c>
@@ -2689,8 +3475,14 @@
         <v>6</v>
       </c>
       <c r="D140" s="2"/>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>137</v>
       </c>
@@ -2701,8 +3493,14 @@
         <v>142</v>
       </c>
       <c r="D141" s="2"/>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>138</v>
       </c>
@@ -2715,8 +3513,14 @@
       <c r="D142" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>139</v>
       </c>
@@ -2727,8 +3531,14 @@
         <v>6</v>
       </c>
       <c r="D143" s="2"/>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>140</v>
       </c>
@@ -2741,8 +3551,14 @@
       <c r="D144" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>141</v>
       </c>
@@ -2753,8 +3569,14 @@
         <v>6</v>
       </c>
       <c r="D145" s="2"/>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>143</v>
       </c>
@@ -2767,8 +3589,14 @@
       <c r="D146" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>144</v>
       </c>
@@ -2777,6 +3605,12 @@
       </c>
       <c r="C147" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/source/spreadsheets/Neoverse_for_Claude.xlsx
+++ b/source/spreadsheets/Neoverse_for_Claude.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cmestes87/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F05B0A-3873-CA4B-8E68-CA8532B5C801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8553947-3CDE-0046-AF16-3B19052760DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{BF29D5B1-F294-134E-8F7B-70D5B4D848F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="153">
   <si>
     <t>Neoverse Interactive Edition</t>
   </si>
@@ -492,6 +492,12 @@
   </si>
   <si>
     <t>Feature</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Photo Pop</t>
   </si>
 </sst>
 </file>
@@ -878,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7152A363-982E-1044-8657-DA2C0F17B383}">
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
@@ -887,7 +893,7 @@
     <col min="4" max="6" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -909,13 +915,16 @@
       <c r="H1" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -937,8 +946,11 @@
       <c r="H3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -957,8 +969,11 @@
       <c r="H4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -983,8 +998,11 @@
       <c r="H5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>54</v>
       </c>
@@ -1006,8 +1024,11 @@
       <c r="H6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -1026,8 +1047,11 @@
       <c r="H7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>56</v>
       </c>
@@ -1046,8 +1070,11 @@
       <c r="H8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -1066,8 +1093,11 @@
       <c r="H9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -1086,8 +1116,11 @@
       <c r="H10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -1106,8 +1139,11 @@
       <c r="H11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1126,8 +1162,11 @@
       <c r="H12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -1146,8 +1185,11 @@
       <c r="H13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -1166,8 +1208,11 @@
       <c r="H14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -1186,8 +1231,11 @@
       <c r="H15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>64</v>
       </c>
@@ -1206,8 +1254,11 @@
       <c r="H16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>65</v>
       </c>
@@ -1229,8 +1280,11 @@
       <c r="H17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -1252,8 +1306,11 @@
       <c r="H18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -1272,8 +1329,11 @@
       <c r="H19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -1292,8 +1352,11 @@
       <c r="H20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>69</v>
       </c>
@@ -1312,8 +1375,11 @@
       <c r="H21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -1332,8 +1398,11 @@
       <c r="H22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>71</v>
       </c>
@@ -1358,13 +1427,16 @@
       <c r="H23">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -1383,8 +1455,11 @@
       <c r="H26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -1403,8 +1478,11 @@
       <c r="H27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
@@ -1421,8 +1499,11 @@
       <c r="H28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>10</v>
       </c>
@@ -1439,8 +1520,11 @@
       <c r="H29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -1459,8 +1543,11 @@
       <c r="H30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1479,8 +1566,11 @@
       <c r="H31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -1499,8 +1589,11 @@
       <c r="H32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -1519,8 +1612,11 @@
       <c r="H33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -1539,8 +1635,11 @@
       <c r="H34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>16</v>
       </c>
@@ -1557,8 +1656,11 @@
       <c r="H35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -1577,8 +1679,11 @@
       <c r="H36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -1597,8 +1702,11 @@
       <c r="H37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -1617,8 +1725,11 @@
       <c r="H38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>20</v>
       </c>
@@ -1637,8 +1748,11 @@
       <c r="H39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -1657,8 +1771,11 @@
       <c r="H40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>22</v>
       </c>
@@ -1677,8 +1794,11 @@
       <c r="H41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -1697,8 +1817,11 @@
       <c r="H42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>24</v>
       </c>
@@ -1715,8 +1838,11 @@
       <c r="H43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>25</v>
       </c>
@@ -1733,8 +1859,11 @@
       <c r="H44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>26</v>
       </c>
@@ -1753,8 +1882,11 @@
       <c r="H45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>27</v>
       </c>
@@ -1773,8 +1905,11 @@
       <c r="H46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>28</v>
       </c>
@@ -1791,8 +1926,11 @@
       <c r="H47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>29</v>
       </c>
@@ -1811,8 +1949,11 @@
       <c r="H48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>30</v>
       </c>
@@ -1831,8 +1972,11 @@
       <c r="H49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>31</v>
       </c>
@@ -1849,8 +1993,11 @@
       <c r="H50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1869,8 +2016,11 @@
       <c r="H51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>33</v>
       </c>
@@ -1889,8 +2039,11 @@
       <c r="H52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>34</v>
       </c>
@@ -1909,8 +2062,11 @@
       <c r="H53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>35</v>
       </c>
@@ -1929,8 +2085,11 @@
       <c r="H54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>36</v>
       </c>
@@ -1949,8 +2108,11 @@
       <c r="H55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>37</v>
       </c>
@@ -1967,8 +2129,11 @@
       <c r="H56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>38</v>
       </c>
@@ -1987,8 +2152,11 @@
       <c r="H57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>39</v>
       </c>
@@ -2007,8 +2175,11 @@
       <c r="H58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -2027,8 +2198,11 @@
       <c r="H59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>41</v>
       </c>
@@ -2047,8 +2221,11 @@
       <c r="H60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>42</v>
       </c>
@@ -2067,8 +2244,11 @@
       <c r="H61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>43</v>
       </c>
@@ -2087,8 +2267,11 @@
       <c r="H62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>44</v>
       </c>
@@ -2107,8 +2290,11 @@
       <c r="H63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>45</v>
       </c>
@@ -2127,8 +2313,11 @@
       <c r="H64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>46</v>
       </c>
@@ -2147,8 +2336,11 @@
       <c r="H65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>47</v>
       </c>
@@ -2167,8 +2359,11 @@
       <c r="H66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>48</v>
       </c>
@@ -2187,8 +2382,11 @@
       <c r="H67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>49</v>
       </c>
@@ -2207,13 +2405,16 @@
       <c r="H68">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -2232,8 +2433,11 @@
       <c r="H71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -2252,8 +2456,11 @@
       <c r="H72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>75</v>
       </c>
@@ -2270,8 +2477,11 @@
       <c r="H73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -2290,8 +2500,11 @@
       <c r="H74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -2310,8 +2523,11 @@
       <c r="H75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -2330,8 +2546,11 @@
       <c r="H76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -2350,8 +2569,11 @@
       <c r="H77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -2370,8 +2592,11 @@
       <c r="H78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>81</v>
       </c>
@@ -2388,8 +2613,11 @@
       <c r="H79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -2408,8 +2636,11 @@
       <c r="H80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>83</v>
       </c>
@@ -2426,8 +2657,11 @@
       <c r="H81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>84</v>
       </c>
@@ -2444,8 +2678,11 @@
       <c r="H82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -2464,8 +2701,11 @@
       <c r="H83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -2484,8 +2724,11 @@
       <c r="H84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -2504,8 +2747,11 @@
       <c r="H85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -2524,8 +2770,11 @@
       <c r="H86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>89</v>
       </c>
@@ -2544,8 +2793,11 @@
       <c r="H87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>90</v>
       </c>
@@ -2564,8 +2816,11 @@
       <c r="H88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -2584,8 +2839,11 @@
       <c r="H89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>92</v>
       </c>
@@ -2602,8 +2860,11 @@
       <c r="H90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>93</v>
       </c>
@@ -2620,8 +2881,11 @@
       <c r="H91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -2640,8 +2904,11 @@
       <c r="H92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -2660,8 +2927,11 @@
       <c r="H93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>96</v>
       </c>
@@ -2678,8 +2948,11 @@
       <c r="H94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -2698,8 +2971,11 @@
       <c r="H95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>98</v>
       </c>
@@ -2716,8 +2992,11 @@
       <c r="H96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>99</v>
       </c>
@@ -2734,8 +3013,11 @@
       <c r="H97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>100</v>
       </c>
@@ -2754,8 +3036,11 @@
       <c r="H98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>101</v>
       </c>
@@ -2772,8 +3057,11 @@
       <c r="H99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>145</v>
       </c>
@@ -2792,8 +3080,11 @@
       <c r="H100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>146</v>
       </c>
@@ -2812,8 +3103,11 @@
       <c r="H101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>147</v>
       </c>
@@ -2832,8 +3126,11 @@
       <c r="H102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -2852,8 +3149,11 @@
       <c r="H103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -2872,8 +3172,11 @@
       <c r="H104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -2892,13 +3195,16 @@
       <c r="H105">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>106</v>
       </c>
@@ -2917,8 +3223,11 @@
       <c r="H108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -2937,8 +3246,11 @@
       <c r="H109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -2957,8 +3269,11 @@
       <c r="H110">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -2977,8 +3292,11 @@
       <c r="H111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>110</v>
       </c>
@@ -2997,8 +3315,11 @@
       <c r="H112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>111</v>
       </c>
@@ -3017,8 +3338,11 @@
       <c r="H113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>112</v>
       </c>
@@ -3037,8 +3361,11 @@
       <c r="H114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>113</v>
       </c>
@@ -3057,8 +3384,11 @@
       <c r="H115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>114</v>
       </c>
@@ -3077,8 +3407,11 @@
       <c r="H116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>115</v>
       </c>
@@ -3097,8 +3430,11 @@
       <c r="H117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>116</v>
       </c>
@@ -3117,13 +3453,16 @@
       <c r="H118">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>118</v>
       </c>
@@ -3142,8 +3481,11 @@
       <c r="H121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>119</v>
       </c>
@@ -3162,8 +3504,11 @@
       <c r="H122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>120</v>
       </c>
@@ -3182,8 +3527,11 @@
       <c r="H123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>121</v>
       </c>
@@ -3200,8 +3548,11 @@
       <c r="H124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>122</v>
       </c>
@@ -3220,8 +3571,11 @@
       <c r="H125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>123</v>
       </c>
@@ -3238,8 +3592,11 @@
       <c r="H126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>124</v>
       </c>
@@ -3258,8 +3615,11 @@
       <c r="H127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>125</v>
       </c>
@@ -3278,8 +3638,11 @@
       <c r="H128">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>126</v>
       </c>
@@ -3298,8 +3661,11 @@
       <c r="H129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>127</v>
       </c>
@@ -3318,8 +3684,11 @@
       <c r="H130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>128</v>
       </c>
@@ -3338,8 +3707,11 @@
       <c r="H131">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>129</v>
       </c>
@@ -3358,8 +3730,11 @@
       <c r="H132">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>130</v>
       </c>
@@ -3378,8 +3753,11 @@
       <c r="H133">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>131</v>
       </c>
@@ -3398,8 +3776,11 @@
       <c r="H134">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>132</v>
       </c>
@@ -3418,13 +3799,16 @@
       <c r="H135">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>134</v>
       </c>
@@ -3443,8 +3827,11 @@
       <c r="H138">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>135</v>
       </c>
@@ -3463,8 +3850,11 @@
       <c r="H139">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>136</v>
       </c>
@@ -3481,8 +3871,11 @@
       <c r="H140">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>137</v>
       </c>
@@ -3499,8 +3892,11 @@
       <c r="H141">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>138</v>
       </c>
@@ -3519,8 +3915,11 @@
       <c r="H142">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>139</v>
       </c>
@@ -3537,8 +3936,11 @@
       <c r="H143">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>140</v>
       </c>
@@ -3557,8 +3959,11 @@
       <c r="H144">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>141</v>
       </c>
@@ -3575,8 +3980,11 @@
       <c r="H145">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>143</v>
       </c>
@@ -3595,8 +4003,11 @@
       <c r="H146">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>144</v>
       </c>
@@ -3610,6 +4021,32 @@
         <v>0</v>
       </c>
       <c r="H147">
+        <v>1</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>152</v>
+      </c>
+      <c r="B148" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" t="s">
+        <v>6</v>
+      </c>
+      <c r="D148" t="s">
+        <v>7</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>1</v>
+      </c>
+      <c r="I148">
         <v>1</v>
       </c>
     </row>

--- a/source/spreadsheets/Neoverse_for_Claude.xlsx
+++ b/source/spreadsheets/Neoverse_for_Claude.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cmestes87/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8553947-3CDE-0046-AF16-3B19052760DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6D2337-9586-9642-898E-7CCF733D0A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{BF29D5B1-F294-134E-8F7B-70D5B4D848F8}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{BF29D5B1-F294-134E-8F7B-70D5B4D848F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 (2)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="162">
   <si>
     <t>Neoverse Interactive Edition</t>
   </si>
@@ -498,6 +498,33 @@
   </si>
   <si>
     <t>Photo Pop</t>
+  </si>
+  <si>
+    <t>TD End Zone</t>
+  </si>
+  <si>
+    <t>TD Fourth Down</t>
+  </si>
+  <si>
+    <t>TD Game Day</t>
+  </si>
+  <si>
+    <t>HR Full Count</t>
+  </si>
+  <si>
+    <t>HR Grand Slam</t>
+  </si>
+  <si>
+    <t>HR Stolen Base</t>
+  </si>
+  <si>
+    <t>Festive Skulls</t>
+  </si>
+  <si>
+    <t>Halloween Dance</t>
+  </si>
+  <si>
+    <t>Magic Triangle Classic</t>
   </si>
 </sst>
 </file>
@@ -884,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7152A363-982E-1044-8657-DA2C0F17B383}">
-  <dimension ref="A1:I148"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
@@ -1731,7 +1758,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -1749,12 +1776,12 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
@@ -1777,7 +1804,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
@@ -1800,126 +1827,128 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>160</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" t="s">
+        <v>7</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>23</v>
       </c>
-      <c r="B42" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
+      <c r="B45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" s="2"/>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="B46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>26</v>
       </c>
-      <c r="B45" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" t="s">
-        <v>7</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47" s="2"/>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
       <c r="G47">
         <v>1</v>
       </c>
@@ -1932,61 +1961,61 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>29</v>
       </c>
-      <c r="B48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" t="s">
-        <v>7</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>30</v>
-      </c>
-      <c r="B49" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" t="s">
-        <v>7</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="2"/>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" t="s">
+        <v>7</v>
+      </c>
       <c r="G50">
         <v>1</v>
       </c>
@@ -1999,7 +2028,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B51" t="s">
         <v>6</v>
@@ -2021,18 +2050,16 @@
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>33</v>
-      </c>
-      <c r="B52" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" t="s">
-        <v>7</v>
-      </c>
+      <c r="A52" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="2"/>
       <c r="G52">
         <v>1</v>
       </c>
@@ -2045,7 +2072,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
         <v>6</v>
@@ -2068,7 +2095,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
         <v>6</v>
@@ -2091,7 +2118,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B55" t="s">
         <v>6</v>
@@ -2113,16 +2140,18 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" s="2"/>
+      <c r="A56" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" t="s">
+        <v>7</v>
+      </c>
       <c r="G56">
         <v>1</v>
       </c>
@@ -2135,7 +2164,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B57" t="s">
         <v>6</v>
@@ -2157,18 +2186,16 @@
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" t="s">
-        <v>6</v>
-      </c>
-      <c r="D58" t="s">
-        <v>7</v>
-      </c>
+      <c r="A58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="2"/>
       <c r="G58">
         <v>1</v>
       </c>
@@ -2181,7 +2208,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
         <v>6</v>
@@ -2204,7 +2231,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B60" t="s">
         <v>6</v>
@@ -2227,7 +2254,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B61" t="s">
         <v>6</v>
@@ -2250,7 +2277,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B62" t="s">
         <v>6</v>
@@ -2273,7 +2300,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B63" t="s">
         <v>6</v>
@@ -2296,7 +2323,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B64" t="s">
         <v>6</v>
@@ -2319,7 +2346,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B65" t="s">
         <v>6</v>
@@ -2342,7 +2369,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
         <v>6</v>
@@ -2365,7 +2392,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B67" t="s">
         <v>6</v>
@@ -2388,89 +2415,91 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>47</v>
+      </c>
+      <c r="B68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>48</v>
+      </c>
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
         <v>49</v>
       </c>
-      <c r="B68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" t="s">
-        <v>6</v>
-      </c>
-      <c r="D68" t="s">
-        <v>7</v>
-      </c>
-      <c r="G68">
-        <v>1</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
+      <c r="B70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" t="s">
+        <v>7</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
         <v>73</v>
       </c>
-      <c r="B71" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" t="s">
-        <v>6</v>
-      </c>
-      <c r="D71" t="s">
-        <v>7</v>
-      </c>
-      <c r="G71">
-        <v>1</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>74</v>
-      </c>
-      <c r="B72" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" t="s">
-        <v>6</v>
-      </c>
-      <c r="D72" t="s">
-        <v>7</v>
-      </c>
-      <c r="G72">
-        <v>1</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A73" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D73" s="2"/>
+      <c r="B73" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73" t="s">
+        <v>7</v>
+      </c>
       <c r="G73">
         <v>1</v>
       </c>
@@ -2483,7 +2512,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B74" t="s">
         <v>6</v>
@@ -2505,18 +2534,16 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>77</v>
-      </c>
-      <c r="B75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" t="s">
-        <v>6</v>
-      </c>
-      <c r="D75" t="s">
-        <v>7</v>
-      </c>
+      <c r="A75" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="2"/>
       <c r="G75">
         <v>1</v>
       </c>
@@ -2529,7 +2556,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B76" t="s">
         <v>6</v>
@@ -2552,7 +2579,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B77" t="s">
         <v>6</v>
@@ -2575,7 +2602,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B78" t="s">
         <v>6</v>
@@ -2597,16 +2624,18 @@
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A79" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D79" s="2"/>
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" t="s">
+        <v>7</v>
+      </c>
       <c r="G79">
         <v>1</v>
       </c>
@@ -2619,7 +2648,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B80" t="s">
         <v>6</v>
@@ -2642,7 +2671,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>6</v>
@@ -2662,62 +2691,60 @@
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A82" s="2" t="s">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" t="s">
+        <v>7</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D82" s="2"/>
-      <c r="G82">
-        <v>1</v>
-      </c>
-      <c r="H82">
-        <v>0</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>85</v>
-      </c>
-      <c r="B83" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" t="s">
-        <v>6</v>
-      </c>
-      <c r="D83" t="s">
-        <v>7</v>
-      </c>
-      <c r="G83">
-        <v>1</v>
-      </c>
-      <c r="H83">
-        <v>0</v>
-      </c>
-      <c r="I83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>86</v>
-      </c>
-      <c r="B84" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" t="s">
-        <v>6</v>
-      </c>
-      <c r="D84" t="s">
-        <v>7</v>
-      </c>
+      <c r="B84" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" s="2"/>
       <c r="G84">
         <v>1</v>
       </c>
@@ -2730,7 +2757,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
         <v>6</v>
@@ -2753,7 +2780,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
@@ -2776,7 +2803,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B87" t="s">
         <v>6</v>
@@ -2799,7 +2826,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B88" t="s">
         <v>6</v>
@@ -2822,7 +2849,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B89" t="s">
         <v>6</v>
@@ -2844,16 +2871,18 @@
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A90" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D90" s="2"/>
+      <c r="A90" t="s">
+        <v>156</v>
+      </c>
+      <c r="B90" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" t="s">
+        <v>7</v>
+      </c>
       <c r="G90">
         <v>1</v>
       </c>
@@ -2861,20 +2890,22 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A91" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D91" s="2"/>
+      <c r="A91" t="s">
+        <v>157</v>
+      </c>
+      <c r="B91" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" t="s">
+        <v>7</v>
+      </c>
       <c r="G91">
         <v>1</v>
       </c>
@@ -2882,12 +2913,12 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>94</v>
+        <v>158</v>
       </c>
       <c r="B92" t="s">
         <v>6</v>
@@ -2905,12 +2936,12 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B93" t="s">
         <v>6</v>
@@ -2932,16 +2963,18 @@
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A94" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D94" s="2"/>
+      <c r="A94" t="s">
+        <v>91</v>
+      </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" t="s">
+        <v>6</v>
+      </c>
+      <c r="D94" t="s">
+        <v>7</v>
+      </c>
       <c r="G94">
         <v>1</v>
       </c>
@@ -2953,18 +2986,16 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>97</v>
-      </c>
-      <c r="B95" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" t="s">
-        <v>6</v>
-      </c>
-      <c r="D95" t="s">
-        <v>7</v>
-      </c>
+      <c r="A95" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" s="2"/>
       <c r="G95">
         <v>1</v>
       </c>
@@ -2977,7 +3008,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>6</v>
@@ -2997,16 +3028,18 @@
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A97" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D97" s="2"/>
+      <c r="A97" t="s">
+        <v>94</v>
+      </c>
+      <c r="B97" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" t="s">
+        <v>7</v>
+      </c>
       <c r="G97">
         <v>1</v>
       </c>
@@ -3019,7 +3052,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B98" t="s">
         <v>6</v>
@@ -3042,7 +3075,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>6</v>
@@ -3063,7 +3096,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="B100" t="s">
         <v>6</v>
@@ -3081,22 +3114,20 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>146</v>
-      </c>
-      <c r="B101" t="s">
-        <v>6</v>
-      </c>
-      <c r="C101" t="s">
-        <v>6</v>
-      </c>
-      <c r="D101" t="s">
-        <v>7</v>
-      </c>
+      <c r="A101" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" s="2"/>
       <c r="G101">
         <v>1</v>
       </c>
@@ -3104,22 +3135,20 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>147</v>
-      </c>
-      <c r="B102" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102" t="s">
-        <v>6</v>
-      </c>
-      <c r="D102" t="s">
-        <v>7</v>
-      </c>
+      <c r="A102" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" s="2"/>
       <c r="G102">
         <v>1</v>
       </c>
@@ -3127,12 +3156,12 @@
         <v>0</v>
       </c>
       <c r="I102">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B103" t="s">
         <v>6</v>
@@ -3154,18 +3183,16 @@
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>103</v>
-      </c>
-      <c r="B104" t="s">
-        <v>6</v>
-      </c>
-      <c r="C104" t="s">
-        <v>6</v>
-      </c>
-      <c r="D104" t="s">
-        <v>7</v>
-      </c>
+      <c r="A104" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" s="2"/>
       <c r="G104">
         <v>1</v>
       </c>
@@ -3177,16 +3204,16 @@
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>104</v>
-      </c>
-      <c r="B105" t="s">
-        <v>6</v>
-      </c>
-      <c r="C105" t="s">
-        <v>6</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="A105" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G105">
@@ -3196,17 +3223,58 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A106" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A107" s="1" t="s">
-        <v>105</v>
+      <c r="A107" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="B108" t="s">
         <v>6</v>
@@ -3229,7 +3297,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="B109" t="s">
         <v>6</v>
@@ -3252,7 +3320,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="B110" t="s">
         <v>6</v>
@@ -3275,7 +3343,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B111" t="s">
         <v>6</v>
@@ -3298,13 +3366,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B112" t="s">
         <v>6</v>
       </c>
       <c r="C112" t="s">
-        <v>142</v>
+        <v>6</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -3321,7 +3389,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B113" t="s">
         <v>6</v>
@@ -3342,55 +3410,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>112</v>
-      </c>
-      <c r="B114" t="s">
-        <v>6</v>
-      </c>
-      <c r="C114" t="s">
-        <v>142</v>
-      </c>
-      <c r="D114" t="s">
-        <v>7</v>
-      </c>
-      <c r="G114">
-        <v>1</v>
-      </c>
-      <c r="H114">
-        <v>0</v>
-      </c>
-      <c r="I114">
-        <v>0</v>
-      </c>
-    </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>113</v>
-      </c>
-      <c r="B115" t="s">
-        <v>6</v>
-      </c>
-      <c r="C115" t="s">
-        <v>6</v>
-      </c>
-      <c r="D115" t="s">
-        <v>7</v>
-      </c>
-      <c r="G115">
-        <v>1</v>
-      </c>
-      <c r="H115">
-        <v>0</v>
-      </c>
-      <c r="I115">
-        <v>0</v>
+      <c r="A115" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B116" t="s">
         <v>6</v>
@@ -3413,7 +3440,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B117" t="s">
         <v>6</v>
@@ -3436,7 +3463,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="B118" t="s">
         <v>6</v>
@@ -3454,23 +3481,64 @@
         <v>0</v>
       </c>
       <c r="I118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>108</v>
+      </c>
+      <c r="B119" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" t="s">
+        <v>6</v>
+      </c>
+      <c r="D119" t="s">
+        <v>7</v>
+      </c>
+      <c r="G119">
+        <v>1</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A120" s="1" t="s">
-        <v>117</v>
+      <c r="A120" t="s">
+        <v>109</v>
+      </c>
+      <c r="B120" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" t="s">
+        <v>7</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B121" t="s">
         <v>6</v>
       </c>
       <c r="C121" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -3487,7 +3555,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B122" t="s">
         <v>6</v>
@@ -3510,13 +3578,13 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B123" t="s">
         <v>6</v>
       </c>
       <c r="C123" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -3532,16 +3600,18 @@
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A124" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D124" s="2"/>
+      <c r="A124" t="s">
+        <v>113</v>
+      </c>
+      <c r="B124" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" t="s">
+        <v>6</v>
+      </c>
+      <c r="D124" t="s">
+        <v>7</v>
+      </c>
       <c r="G124">
         <v>1</v>
       </c>
@@ -3554,7 +3624,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B125" t="s">
         <v>6</v>
@@ -3576,16 +3646,18 @@
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A126" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D126" s="2"/>
+      <c r="A126" t="s">
+        <v>115</v>
+      </c>
+      <c r="B126" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" t="s">
+        <v>6</v>
+      </c>
+      <c r="D126" t="s">
+        <v>7</v>
+      </c>
       <c r="G126">
         <v>1</v>
       </c>
@@ -3598,7 +3670,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B127" t="s">
         <v>6</v>
@@ -3619,55 +3691,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
-        <v>125</v>
-      </c>
-      <c r="B128" t="s">
-        <v>6</v>
-      </c>
-      <c r="C128" t="s">
-        <v>6</v>
-      </c>
-      <c r="D128" t="s">
-        <v>7</v>
-      </c>
-      <c r="G128">
-        <v>1</v>
-      </c>
-      <c r="H128">
-        <v>0</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-    </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
-        <v>126</v>
-      </c>
-      <c r="B129" t="s">
-        <v>6</v>
-      </c>
-      <c r="C129" t="s">
-        <v>6</v>
-      </c>
-      <c r="D129" t="s">
-        <v>7</v>
-      </c>
-      <c r="G129">
-        <v>1</v>
-      </c>
-      <c r="H129">
-        <v>0</v>
-      </c>
-      <c r="I129">
-        <v>0</v>
+      <c r="A129" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B130" t="s">
         <v>6</v>
@@ -3690,7 +3721,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B131" t="s">
         <v>6</v>
@@ -3713,7 +3744,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B132" t="s">
         <v>6</v>
@@ -3735,18 +3766,16 @@
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
-        <v>130</v>
-      </c>
-      <c r="B133" t="s">
-        <v>6</v>
-      </c>
-      <c r="C133" t="s">
-        <v>6</v>
-      </c>
-      <c r="D133" t="s">
-        <v>7</v>
-      </c>
+      <c r="A133" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D133" s="2"/>
       <c r="G133">
         <v>1</v>
       </c>
@@ -3759,7 +3788,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B134" t="s">
         <v>6</v>
@@ -3781,18 +3810,16 @@
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
-        <v>132</v>
-      </c>
-      <c r="B135" t="s">
-        <v>6</v>
-      </c>
-      <c r="C135" t="s">
-        <v>6</v>
-      </c>
-      <c r="D135" t="s">
-        <v>7</v>
-      </c>
+      <c r="A135" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" s="2"/>
       <c r="G135">
         <v>1</v>
       </c>
@@ -3803,29 +3830,70 @@
         <v>0</v>
       </c>
     </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>124</v>
+      </c>
+      <c r="B136" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" t="s">
+        <v>6</v>
+      </c>
+      <c r="D136" t="s">
+        <v>7</v>
+      </c>
+      <c r="G136">
+        <v>1</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+    </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A137" s="1" t="s">
-        <v>133</v>
+      <c r="A137" t="s">
+        <v>125</v>
+      </c>
+      <c r="B137" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" t="s">
+        <v>6</v>
+      </c>
+      <c r="D137" t="s">
+        <v>7</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B138" t="s">
         <v>6</v>
       </c>
       <c r="C138" t="s">
-        <v>142</v>
+        <v>6</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
       </c>
       <c r="G138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138">
         <v>0</v>
@@ -3833,64 +3901,68 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B139" t="s">
         <v>6</v>
       </c>
       <c r="C139" t="s">
-        <v>142</v>
+        <v>6</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
       </c>
       <c r="G139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139">
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A140" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D140" s="2"/>
+      <c r="A140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B140" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" t="s">
+        <v>6</v>
+      </c>
+      <c r="D140" t="s">
+        <v>7</v>
+      </c>
       <c r="G140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140">
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A141" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D141" s="2"/>
+      <c r="A141" t="s">
+        <v>129</v>
+      </c>
+      <c r="B141" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" t="s">
+        <v>6</v>
+      </c>
+      <c r="D141" t="s">
+        <v>7</v>
+      </c>
       <c r="G141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -3898,7 +3970,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B142" t="s">
         <v>6</v>
@@ -3910,31 +3982,33 @@
         <v>7</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142">
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A143" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D143" s="2"/>
+      <c r="A143" t="s">
+        <v>131</v>
+      </c>
+      <c r="B143" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" t="s">
+        <v>6</v>
+      </c>
+      <c r="D143" t="s">
+        <v>7</v>
+      </c>
       <c r="G143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I143">
         <v>0</v>
@@ -3942,7 +4016,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B144" t="s">
         <v>6</v>
@@ -3954,68 +4028,32 @@
         <v>7</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144">
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A145" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D145" s="2"/>
-      <c r="G145">
-        <v>0</v>
-      </c>
-      <c r="H145">
-        <v>1</v>
-      </c>
-      <c r="I145">
-        <v>0</v>
-      </c>
-    </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
-        <v>143</v>
-      </c>
-      <c r="B146" t="s">
-        <v>6</v>
-      </c>
-      <c r="C146" t="s">
-        <v>6</v>
-      </c>
-      <c r="D146" t="s">
-        <v>7</v>
-      </c>
-      <c r="G146">
-        <v>0</v>
-      </c>
-      <c r="H146">
-        <v>1</v>
-      </c>
-      <c r="I146">
-        <v>0</v>
+      <c r="A146" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A147" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>6</v>
+      <c r="A147" t="s">
+        <v>134</v>
+      </c>
+      <c r="B147" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" t="s">
+        <v>142</v>
+      </c>
+      <c r="D147" t="s">
+        <v>7</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -4029,24 +4067,220 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
+        <v>135</v>
+      </c>
+      <c r="B148" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" t="s">
+        <v>142</v>
+      </c>
+      <c r="D148" t="s">
+        <v>7</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>1</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A149" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D149" s="2"/>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>1</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A150" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D150" s="2"/>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>1</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>138</v>
+      </c>
+      <c r="B151" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" t="s">
+        <v>6</v>
+      </c>
+      <c r="D151" t="s">
+        <v>7</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A152" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D152" s="2"/>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>1</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>140</v>
+      </c>
+      <c r="B153" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" t="s">
+        <v>6</v>
+      </c>
+      <c r="D153" t="s">
+        <v>7</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>1</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A154" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D154" s="2"/>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>1</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>143</v>
+      </c>
+      <c r="B155" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" t="s">
+        <v>6</v>
+      </c>
+      <c r="D155" t="s">
+        <v>7</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>1</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A156" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>1</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
         <v>152</v>
       </c>
-      <c r="B148" t="s">
-        <v>6</v>
-      </c>
-      <c r="C148" t="s">
-        <v>6</v>
-      </c>
-      <c r="D148" t="s">
-        <v>7</v>
-      </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-      <c r="H148">
-        <v>1</v>
-      </c>
-      <c r="I148">
+      <c r="B157" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" t="s">
+        <v>6</v>
+      </c>
+      <c r="D157" t="s">
+        <v>7</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>1</v>
+      </c>
+      <c r="I157">
         <v>1</v>
       </c>
     </row>

--- a/source/spreadsheets/Neoverse_for_Claude.xlsx
+++ b/source/spreadsheets/Neoverse_for_Claude.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cmestes87/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6D2337-9586-9642-898E-7CCF733D0A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371E62B2-5E5D-9649-A9BE-1B62FFEF6F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{BF29D5B1-F294-134E-8F7B-70D5B4D848F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="156">
   <si>
     <t>Neoverse Interactive Edition</t>
   </si>
@@ -498,24 +498,6 @@
   </si>
   <si>
     <t>Photo Pop</t>
-  </si>
-  <si>
-    <t>TD End Zone</t>
-  </si>
-  <si>
-    <t>TD Fourth Down</t>
-  </si>
-  <si>
-    <t>TD Game Day</t>
-  </si>
-  <si>
-    <t>HR Full Count</t>
-  </si>
-  <si>
-    <t>HR Grand Slam</t>
-  </si>
-  <si>
-    <t>HR Stolen Base</t>
   </si>
   <si>
     <t>Festive Skulls</t>
@@ -911,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7152A363-982E-1044-8657-DA2C0F17B383}">
-  <dimension ref="A1:I157"/>
+  <dimension ref="A1:I151"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
@@ -1758,7 +1740,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -1850,7 +1832,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
@@ -2872,7 +2854,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>156</v>
+        <v>90</v>
       </c>
       <c r="B90" t="s">
         <v>6</v>
@@ -2890,12 +2872,12 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="B91" t="s">
         <v>6</v>
@@ -2913,22 +2895,20 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>158</v>
-      </c>
-      <c r="B92" t="s">
-        <v>6</v>
-      </c>
-      <c r="C92" t="s">
-        <v>6</v>
-      </c>
-      <c r="D92" t="s">
-        <v>7</v>
-      </c>
+      <c r="A92" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" s="2"/>
       <c r="G92">
         <v>1</v>
       </c>
@@ -2936,22 +2916,20 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>90</v>
-      </c>
-      <c r="B93" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" t="s">
-        <v>6</v>
-      </c>
-      <c r="D93" t="s">
-        <v>7</v>
-      </c>
+      <c r="A93" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D93" s="2"/>
       <c r="G93">
         <v>1</v>
       </c>
@@ -2964,7 +2942,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B94" t="s">
         <v>6</v>
@@ -2986,16 +2964,18 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A95" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D95" s="2"/>
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+      <c r="B95" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" t="s">
+        <v>7</v>
+      </c>
       <c r="G95">
         <v>1</v>
       </c>
@@ -3008,7 +2988,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>6</v>
@@ -3029,7 +3009,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B97" t="s">
         <v>6</v>
@@ -3051,18 +3031,16 @@
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>95</v>
-      </c>
-      <c r="B98" t="s">
-        <v>6</v>
-      </c>
-      <c r="C98" t="s">
-        <v>6</v>
-      </c>
-      <c r="D98" t="s">
-        <v>7</v>
-      </c>
+      <c r="A98" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98" s="2"/>
       <c r="G98">
         <v>1</v>
       </c>
@@ -3075,7 +3053,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>6</v>
@@ -3096,7 +3074,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B100" t="s">
         <v>6</v>
@@ -3119,7 +3097,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>6</v>
@@ -3139,16 +3117,18 @@
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A102" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D102" s="2"/>
+      <c r="A102" t="s">
+        <v>145</v>
+      </c>
+      <c r="B102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" t="s">
+        <v>7</v>
+      </c>
       <c r="G102">
         <v>1</v>
       </c>
@@ -3161,7 +3141,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="B103" t="s">
         <v>6</v>
@@ -3183,16 +3163,18 @@
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A104" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D104" s="2"/>
+      <c r="A104" t="s">
+        <v>147</v>
+      </c>
+      <c r="B104" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" t="s">
+        <v>7</v>
+      </c>
       <c r="G104">
         <v>1</v>
       </c>
@@ -3204,16 +3186,16 @@
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A105" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D105" s="2" t="s">
+      <c r="A105" t="s">
+        <v>102</v>
+      </c>
+      <c r="B105" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" t="s">
         <v>7</v>
       </c>
       <c r="G105">
@@ -3223,20 +3205,20 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A106" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D106" s="2" t="s">
+      <c r="A106" t="s">
+        <v>103</v>
+      </c>
+      <c r="B106" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" t="s">
+        <v>6</v>
+      </c>
+      <c r="D106" t="s">
         <v>7</v>
       </c>
       <c r="G106">
@@ -3246,20 +3228,20 @@
         <v>0</v>
       </c>
       <c r="I106">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A107" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D107" s="2" t="s">
+      <c r="A107" t="s">
+        <v>104</v>
+      </c>
+      <c r="B107" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" t="s">
         <v>7</v>
       </c>
       <c r="G107">
@@ -3269,58 +3251,17 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
-        <v>145</v>
-      </c>
-      <c r="B108" t="s">
-        <v>6</v>
-      </c>
-      <c r="C108" t="s">
-        <v>6</v>
-      </c>
-      <c r="D108" t="s">
-        <v>7</v>
-      </c>
-      <c r="G108">
-        <v>1</v>
-      </c>
-      <c r="H108">
-        <v>0</v>
-      </c>
-      <c r="I108">
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
-        <v>146</v>
-      </c>
-      <c r="B109" t="s">
-        <v>6</v>
-      </c>
-      <c r="C109" t="s">
-        <v>6</v>
-      </c>
-      <c r="D109" t="s">
-        <v>7</v>
-      </c>
-      <c r="G109">
-        <v>1</v>
-      </c>
-      <c r="H109">
-        <v>0</v>
-      </c>
-      <c r="I109">
-        <v>0</v>
+      <c r="A109" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="B110" t="s">
         <v>6</v>
@@ -3343,7 +3284,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B111" t="s">
         <v>6</v>
@@ -3366,7 +3307,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="B112" t="s">
         <v>6</v>
@@ -3384,12 +3325,12 @@
         <v>0</v>
       </c>
       <c r="I112">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B113" t="s">
         <v>6</v>
@@ -3410,14 +3351,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>109</v>
+      </c>
+      <c r="B114" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" t="s">
+        <v>6</v>
+      </c>
+      <c r="D114" t="s">
+        <v>7</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+    </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A115" s="1" t="s">
-        <v>105</v>
+      <c r="A115" t="s">
+        <v>110</v>
+      </c>
+      <c r="B115" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" t="s">
+        <v>142</v>
+      </c>
+      <c r="D115" t="s">
+        <v>7</v>
+      </c>
+      <c r="G115">
+        <v>1</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B116" t="s">
         <v>6</v>
@@ -3440,13 +3422,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B117" t="s">
         <v>6</v>
       </c>
       <c r="C117" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -3463,7 +3445,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="B118" t="s">
         <v>6</v>
@@ -3481,12 +3463,12 @@
         <v>0</v>
       </c>
       <c r="I118">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B119" t="s">
         <v>6</v>
@@ -3509,7 +3491,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B120" t="s">
         <v>6</v>
@@ -3532,13 +3514,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B121" t="s">
         <v>6</v>
       </c>
       <c r="C121" t="s">
-        <v>142</v>
+        <v>6</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -3553,55 +3535,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
-        <v>111</v>
-      </c>
-      <c r="B122" t="s">
-        <v>6</v>
-      </c>
-      <c r="C122" t="s">
-        <v>6</v>
-      </c>
-      <c r="D122" t="s">
-        <v>7</v>
-      </c>
-      <c r="G122">
-        <v>1</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-    </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
-        <v>112</v>
-      </c>
-      <c r="B123" t="s">
-        <v>6</v>
-      </c>
-      <c r="C123" t="s">
-        <v>142</v>
-      </c>
-      <c r="D123" t="s">
-        <v>7</v>
-      </c>
-      <c r="G123">
-        <v>1</v>
-      </c>
-      <c r="H123">
-        <v>0</v>
-      </c>
-      <c r="I123">
-        <v>0</v>
+      <c r="A123" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B124" t="s">
         <v>6</v>
@@ -3624,7 +3565,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B125" t="s">
         <v>6</v>
@@ -3647,7 +3588,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B126" t="s">
         <v>6</v>
@@ -3669,18 +3610,16 @@
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
-        <v>116</v>
-      </c>
-      <c r="B127" t="s">
-        <v>6</v>
-      </c>
-      <c r="C127" t="s">
-        <v>6</v>
-      </c>
-      <c r="D127" t="s">
-        <v>7</v>
-      </c>
+      <c r="A127" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D127" s="2"/>
       <c r="G127">
         <v>1</v>
       </c>
@@ -3691,14 +3630,53 @@
         <v>0</v>
       </c>
     </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>122</v>
+      </c>
+      <c r="B128" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" t="s">
+        <v>6</v>
+      </c>
+      <c r="D128" t="s">
+        <v>7</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+    </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A129" s="1" t="s">
-        <v>117</v>
+      <c r="A129" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D129" s="2"/>
+      <c r="G129">
+        <v>1</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B130" t="s">
         <v>6</v>
@@ -3721,7 +3699,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B131" t="s">
         <v>6</v>
@@ -3744,7 +3722,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B132" t="s">
         <v>6</v>
@@ -3766,16 +3744,18 @@
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A133" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D133" s="2"/>
+      <c r="A133" t="s">
+        <v>127</v>
+      </c>
+      <c r="B133" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" t="s">
+        <v>6</v>
+      </c>
+      <c r="D133" t="s">
+        <v>7</v>
+      </c>
       <c r="G133">
         <v>1</v>
       </c>
@@ -3788,7 +3768,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B134" t="s">
         <v>6</v>
@@ -3810,16 +3790,18 @@
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A135" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D135" s="2"/>
+      <c r="A135" t="s">
+        <v>129</v>
+      </c>
+      <c r="B135" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" t="s">
+        <v>7</v>
+      </c>
       <c r="G135">
         <v>1</v>
       </c>
@@ -3832,7 +3814,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B136" t="s">
         <v>6</v>
@@ -3855,7 +3837,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B137" t="s">
         <v>6</v>
@@ -3878,7 +3860,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B138" t="s">
         <v>6</v>
@@ -3899,70 +3881,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
-        <v>127</v>
-      </c>
-      <c r="B139" t="s">
-        <v>6</v>
-      </c>
-      <c r="C139" t="s">
-        <v>6</v>
-      </c>
-      <c r="D139" t="s">
-        <v>7</v>
-      </c>
-      <c r="G139">
-        <v>1</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-    </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
-        <v>128</v>
-      </c>
-      <c r="B140" t="s">
-        <v>6</v>
-      </c>
-      <c r="C140" t="s">
-        <v>6</v>
-      </c>
-      <c r="D140" t="s">
-        <v>7</v>
-      </c>
-      <c r="G140">
-        <v>1</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
+      <c r="A140" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B141" t="s">
         <v>6</v>
       </c>
       <c r="C141" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
       </c>
       <c r="G141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -3970,87 +3911,122 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B142" t="s">
         <v>6</v>
       </c>
       <c r="C142" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
       </c>
       <c r="G142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I142">
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>131</v>
-      </c>
-      <c r="B143" t="s">
-        <v>6</v>
-      </c>
-      <c r="C143" t="s">
-        <v>6</v>
-      </c>
-      <c r="D143" t="s">
-        <v>7</v>
-      </c>
+      <c r="A143" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D143" s="2"/>
       <c r="G143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143">
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>132</v>
-      </c>
-      <c r="B144" t="s">
-        <v>6</v>
-      </c>
-      <c r="C144" t="s">
-        <v>6</v>
-      </c>
-      <c r="D144" t="s">
-        <v>7</v>
-      </c>
+      <c r="A144" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D144" s="2"/>
       <c r="G144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144">
         <v>0</v>
       </c>
     </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>138</v>
+      </c>
+      <c r="B145" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" t="s">
+        <v>6</v>
+      </c>
+      <c r="D145" t="s">
+        <v>7</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+    </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A146" s="1" t="s">
-        <v>133</v>
+      <c r="A146" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D146" s="2"/>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>1</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B147" t="s">
         <v>6</v>
       </c>
       <c r="C147" t="s">
-        <v>142</v>
+        <v>6</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -4066,18 +4042,16 @@
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
-        <v>135</v>
-      </c>
-      <c r="B148" t="s">
-        <v>6</v>
-      </c>
-      <c r="C148" t="s">
-        <v>142</v>
-      </c>
-      <c r="D148" t="s">
-        <v>7</v>
-      </c>
+      <c r="A148" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D148" s="2"/>
       <c r="G148">
         <v>0</v>
       </c>
@@ -4089,16 +4063,18 @@
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A149" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D149" s="2"/>
+      <c r="A149" t="s">
+        <v>143</v>
+      </c>
+      <c r="B149" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" t="s">
+        <v>6</v>
+      </c>
+      <c r="D149" t="s">
+        <v>7</v>
+      </c>
       <c r="G149">
         <v>0</v>
       </c>
@@ -4111,15 +4087,14 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D150" s="2"/>
+        <v>6</v>
+      </c>
       <c r="G150">
         <v>0</v>
       </c>
@@ -4132,7 +4107,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="B151" t="s">
         <v>6</v>
@@ -4150,137 +4125,6 @@
         <v>1</v>
       </c>
       <c r="I151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A152" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D152" s="2"/>
-      <c r="G152">
-        <v>0</v>
-      </c>
-      <c r="H152">
-        <v>1</v>
-      </c>
-      <c r="I152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
-        <v>140</v>
-      </c>
-      <c r="B153" t="s">
-        <v>6</v>
-      </c>
-      <c r="C153" t="s">
-        <v>6</v>
-      </c>
-      <c r="D153" t="s">
-        <v>7</v>
-      </c>
-      <c r="G153">
-        <v>0</v>
-      </c>
-      <c r="H153">
-        <v>1</v>
-      </c>
-      <c r="I153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A154" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D154" s="2"/>
-      <c r="G154">
-        <v>0</v>
-      </c>
-      <c r="H154">
-        <v>1</v>
-      </c>
-      <c r="I154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
-        <v>143</v>
-      </c>
-      <c r="B155" t="s">
-        <v>6</v>
-      </c>
-      <c r="C155" t="s">
-        <v>6</v>
-      </c>
-      <c r="D155" t="s">
-        <v>7</v>
-      </c>
-      <c r="G155">
-        <v>0</v>
-      </c>
-      <c r="H155">
-        <v>1</v>
-      </c>
-      <c r="I155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A156" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G156">
-        <v>0</v>
-      </c>
-      <c r="H156">
-        <v>1</v>
-      </c>
-      <c r="I156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>152</v>
-      </c>
-      <c r="B157" t="s">
-        <v>6</v>
-      </c>
-      <c r="C157" t="s">
-        <v>6</v>
-      </c>
-      <c r="D157" t="s">
-        <v>7</v>
-      </c>
-      <c r="G157">
-        <v>0</v>
-      </c>
-      <c r="H157">
-        <v>1</v>
-      </c>
-      <c r="I157">
         <v>1</v>
       </c>
     </row>
